--- a/artfynd/A 25651-2019 artfynd.xlsx
+++ b/artfynd/A 25651-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25651-2019 artfynd.xlsx
+++ b/artfynd/A 25651-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>71933997</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
+        <v>97847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729806.9530465992</v>
+        <v>729807</v>
       </c>
       <c r="R2" t="n">
-        <v>7242280.907336424</v>
+        <v>7242281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-01-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-01-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
